--- a/request_forms/028_workstation_privacy_shield_enrollment_form--request_forms.xlsx
+++ b/request_forms/028_workstation_privacy_shield_enrollment_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1079,8 +1079,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'front_desk',_'value':_'front_desk'}</t>
+          <t>front_desk</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Front Desk', 'value': 'Front Desk'}</t>
+          <t>Front Desk</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'back_office',_'value':_'back_office'}</t>
+          <t>back_office</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Back Office', 'value': 'Back Office'}</t>
+          <t>Back Office</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'employee_prophets_company',_'value':_'employee'}</t>
+          <t>employee_prophets_company</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Employee prophets company', 'value': 'Employee'}</t>
+          <t>Employee prophets company</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'it_department',_'value':_'it'}</t>
+          <t>it_department</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'IT Department', 'value': 'IT'}</t>
+          <t>IT Department</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'facility',_'value':_'facility'}</t>
+          <t>facility</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Facility', 'value': 'Facility'}</t>
+          <t>Facility</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'never',_'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Never', 'value': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'after_1_month',_'value':_'after_1_month'}</t>
+          <t>after_1_month</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'After 1 month', 'value': 'After 1 month'}</t>
+          <t>After 1 month</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'after_2_month',_'value':_'after_2_month'}</t>
+          <t>after_2_month</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'After 2 month', 'value': 'After 2 month'}</t>
+          <t>After 2 month</t>
         </is>
       </c>
     </row>
@@ -1363,12 +1363,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'approved',_'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Approved', 'value': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Pending', 'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'rejected',_'value':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Rejected', 'value': 'Rejected'}</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
